--- a/codingame/practice/19_the_river_2/the_river_2.xlsx
+++ b/codingame/practice/19_the_river_2/the_river_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thanos\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\80_git\10_my_code\02_coding-challenges\codingame\practice\19_the_river_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FCC749-97E6-484D-B093-FE787BD8029C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95ADDA23-87DE-4D1F-A2D3-98A79F62027A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10840" yWindow="8910" windowWidth="19180" windowHeight="12430" xr2:uid="{A186F700-683F-4FA3-BDF3-EACCD9B5FBC3}"/>
+    <workbookView xWindow="15330" yWindow="9840" windowWidth="30045" windowHeight="12810" xr2:uid="{A186F700-683F-4FA3-BDF3-EACCD9B5FBC3}"/>
   </bookViews>
   <sheets>
     <sheet name="river1" sheetId="1" r:id="rId1"/>
